--- a/EX2/CPa_effectivenes_pre_vs_post_calibration/Aggregated_Platt_CP_with_CodeBERT4JIT_test_set.xlsx
+++ b/EX2/CPa_effectivenes_pre_vs_post_calibration/Aggregated_Platt_CP_with_CodeBERT4JIT_test_set.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX2\CPa_effectivenes_pre_vs_post_calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D225C5-068B-4E46-9941-1A9ECCEE0C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78406385-002D-49C9-BF57-A42D7B290FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="588" yWindow="576" windowWidth="20760" windowHeight="11664" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OS_alpha_0.05" sheetId="1" r:id="rId1"/>
@@ -291,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -309,7 +309,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1464,7 +1463,7 @@
         <v>0.89482470784641066</v>
       </c>
       <c r="O8" s="4">
-        <f t="shared" si="1"/>
+        <f>F8/1163</f>
         <v>0.9217540842648323</v>
       </c>
       <c r="P8" s="2"/>
@@ -1532,7 +1531,7 @@
         <v>11</v>
       </c>
       <c r="F10" s="2">
-        <v>1173</v>
+        <v>1161</v>
       </c>
       <c r="G10" s="2">
         <v>147</v>
@@ -1553,11 +1552,11 @@
       <c r="M10" s="3"/>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
-        <v>0.88863636363636367</v>
+        <v>0.87954545454545452</v>
       </c>
       <c r="O10" s="4">
-        <f t="shared" si="1"/>
-        <v>1.0085984522785898</v>
+        <f>F10/1163</f>
+        <v>0.99828030954428204</v>
       </c>
       <c r="P10" s="2"/>
     </row>
@@ -1614,7 +1613,7 @@
       </c>
       <c r="F12" s="6">
         <f>AVERAGE(F2:F11)</f>
-        <v>1114.5</v>
+        <v>1113.3</v>
       </c>
       <c r="H12" s="6">
         <f>AVERAGE(H2:H11)</f>
@@ -1626,11 +1625,11 @@
       </c>
       <c r="N12" s="6">
         <f>AVERAGE(N2:N11)</f>
-        <v>0.89444293381671347</v>
+        <v>0.8935338429076225</v>
       </c>
       <c r="O12" s="6">
         <f>AVERAGE(O2:O11)</f>
-        <v>0.95829750644883926</v>
+        <v>0.95726569217540847</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>13</v>
@@ -1656,11 +1655,11 @@
       </c>
       <c r="N13" s="4">
         <f>STDEV(N2:N11)</f>
-        <v>8.866612685433907E-3</v>
+        <v>9.9303438073514091E-3</v>
       </c>
       <c r="O13" s="4">
         <f>STDEV(O2:O11)</f>
-        <v>2.888206908806705E-2</v>
+        <v>2.7008966038714298E-2</v>
       </c>
       <c r="P13" s="8" t="s">
         <v>55</v>
@@ -1721,37 +1720,37 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="9">
+      <c r="A2">
         <v>1331</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2">
         <v>0.86927122464312545</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2">
         <v>16</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2">
         <v>1315</v>
       </c>
-      <c r="E2" s="9">
-        <v>0</v>
-      </c>
-      <c r="F2" s="9">
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>1157</v>
       </c>
-      <c r="G2" s="9">
+      <c r="G2">
         <v>158</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2">
         <v>16</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2">
         <v>1141</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2">
         <v>136</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2">
         <v>22</v>
       </c>
       <c r="L2" s="3"/>
@@ -1767,37 +1766,37 @@
       <c r="P2" s="2"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="9">
+      <c r="A3">
         <v>1331</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3">
         <v>0.84598046581517661</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3">
         <v>44</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3">
         <v>1287</v>
       </c>
-      <c r="E3" s="9">
-        <v>0</v>
-      </c>
-      <c r="F3" s="9">
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>1126</v>
       </c>
-      <c r="G3" s="9">
+      <c r="G3">
         <v>161</v>
       </c>
-      <c r="H3" s="9">
-        <v>0</v>
-      </c>
-      <c r="I3" s="9">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>1126</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3">
         <v>161</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" s="3"/>
@@ -1813,37 +1812,37 @@
       <c r="P3" s="2"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+      <c r="A4">
         <v>1331</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4">
         <v>0.84522915101427498</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4">
         <v>68</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4">
         <v>1263</v>
       </c>
-      <c r="E4" s="9">
-        <v>0</v>
-      </c>
-      <c r="F4" s="9">
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>1125</v>
       </c>
-      <c r="G4" s="9">
+      <c r="G4">
         <v>138</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4">
         <v>1123</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4">
         <v>132</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4">
         <v>6</v>
       </c>
       <c r="L4" s="3"/>
@@ -1859,37 +1858,37 @@
       <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
+      <c r="A5">
         <v>1331</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5">
         <v>0.85800150262960184</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5">
         <v>18</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5">
         <v>1313</v>
       </c>
-      <c r="E5" s="9">
-        <v>0</v>
-      </c>
-      <c r="F5" s="9">
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>1142</v>
       </c>
-      <c r="G5" s="9">
+      <c r="G5">
         <v>171</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5">
         <v>7</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5">
         <v>1135</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5">
         <v>149</v>
       </c>
-      <c r="K5" s="9">
+      <c r="K5">
         <v>22</v>
       </c>
       <c r="L5" s="3"/>
@@ -1905,37 +1904,37 @@
       <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A6" s="9">
+      <c r="A6">
         <v>1331</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6">
         <v>0.8497370398196844</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6">
         <v>57</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6">
         <v>1274</v>
       </c>
-      <c r="E6" s="9">
-        <v>0</v>
-      </c>
-      <c r="F6" s="9">
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>1131</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6">
         <v>143</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6">
         <v>2</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6">
         <v>1129</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6">
         <v>143</v>
       </c>
-      <c r="K6" s="9">
+      <c r="K6">
         <v>0</v>
       </c>
       <c r="L6" s="3"/>
@@ -1951,37 +1950,37 @@
       <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="9">
+      <c r="A7">
         <v>1331</v>
       </c>
-      <c r="B7" s="9">
+      <c r="B7">
         <v>0.84898572501878289</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7">
         <v>49</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7">
         <v>1282</v>
       </c>
-      <c r="E7" s="9">
-        <v>0</v>
-      </c>
-      <c r="F7" s="9">
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>1130</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G7">
         <v>152</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7">
         <v>5</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7">
         <v>1125</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7">
         <v>143</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K7">
         <v>9</v>
       </c>
       <c r="L7" s="3"/>
@@ -1997,37 +1996,37 @@
       <c r="P7" s="2"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="9">
+      <c r="A8">
         <v>1331</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8">
         <v>0.86701728024042068</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8">
         <v>10</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8">
         <v>1321</v>
       </c>
-      <c r="E8" s="9">
-        <v>0</v>
-      </c>
-      <c r="F8" s="9">
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>1154</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G8">
         <v>167</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8">
         <v>7</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8">
         <v>1147</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8">
         <v>151</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8">
         <v>16</v>
       </c>
       <c r="L8" s="3"/>
@@ -2043,37 +2042,37 @@
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="9">
+      <c r="A9">
         <v>1331</v>
       </c>
-      <c r="B9" s="9">
+      <c r="B9">
         <v>0.86626596543951917</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9">
         <v>46</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9">
         <v>1285</v>
       </c>
-      <c r="E9" s="9">
-        <v>0</v>
-      </c>
-      <c r="F9" s="9">
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>1153</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9">
         <v>132</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9">
         <v>3</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9">
         <v>1150</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9">
         <v>126</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9">
         <v>6</v>
       </c>
       <c r="L9" s="3"/>
@@ -2089,37 +2088,37 @@
       <c r="P9" s="2"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="9">
+      <c r="A10">
         <v>1331</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10">
         <v>0.84297520661157022</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10">
         <v>97</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10">
         <v>1234</v>
       </c>
-      <c r="E10" s="9">
-        <v>0</v>
-      </c>
-      <c r="F10" s="9">
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>1122</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10">
         <v>112</v>
       </c>
-      <c r="H10" s="9">
-        <v>0</v>
-      </c>
-      <c r="I10" s="9">
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>1122</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10">
         <v>112</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10">
         <v>0</v>
       </c>
       <c r="L10" s="3"/>
@@ -2135,37 +2134,37 @@
       <c r="P10" s="2"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="9">
+      <c r="A11">
         <v>1331</v>
       </c>
-      <c r="B11" s="9">
+      <c r="B11">
         <v>0.84898572501878289</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11">
         <v>79</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11">
         <v>1252</v>
       </c>
-      <c r="E11" s="9">
-        <v>0</v>
-      </c>
-      <c r="F11" s="9">
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>1130</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11">
         <v>122</v>
       </c>
-      <c r="H11" s="9">
-        <v>0</v>
-      </c>
-      <c r="I11" s="9">
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
         <v>1130</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11">
         <v>122</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11">
         <v>0</v>
       </c>
       <c r="L11" s="3"/>
@@ -2910,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>2386</v>
+        <v>2383</v>
       </c>
       <c r="G2" s="2">
         <v>155</v>
@@ -2931,11 +2930,11 @@
       <c r="M2" s="3"/>
       <c r="N2" s="4">
         <f>F2/D2</f>
-        <v>0.93900039354584808</v>
+        <v>0.93781975600157419</v>
       </c>
       <c r="O2" s="2">
         <f>F2/2384</f>
-        <v>1.0008389261744965</v>
+        <v>0.99958053691275173</v>
       </c>
       <c r="P2" s="2"/>
     </row>
@@ -3360,7 +3359,7 @@
       </c>
       <c r="F12" s="6">
         <f>AVERAGE(F2:F11)</f>
-        <v>2318.9</v>
+        <v>2318.6</v>
       </c>
       <c r="H12" s="6">
         <f>AVERAGE(H2:H11)</f>
@@ -3372,11 +3371,11 @@
       </c>
       <c r="N12" s="6">
         <f>AVERAGE(N2:N11)</f>
-        <v>0.93963206899453033</v>
+        <v>0.93951400524010287</v>
       </c>
       <c r="O12" s="6">
         <f>AVERAGE(O2:O11)</f>
-        <v>0.97269295302013403</v>
+        <v>0.97256711409395957</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>13</v>
@@ -3402,11 +3401,11 @@
       </c>
       <c r="N13" s="4">
         <f>STDEV(N2:N11)</f>
-        <v>4.8910041033421803E-3</v>
+        <v>4.9220971621303572E-3</v>
       </c>
       <c r="O13" s="4">
         <f>STDEV(O2:O11)</f>
-        <v>1.5077933104663453E-2</v>
+        <v>1.4819973792154838E-2</v>
       </c>
       <c r="P13" s="8" t="s">
         <v>55</v>

--- a/EX2/CPa_effectivenes_pre_vs_post_calibration/Aggregated_Platt_CP_with_CodeBERT4JIT_test_set.xlsx
+++ b/EX2/CPa_effectivenes_pre_vs_post_calibration/Aggregated_Platt_CP_with_CodeBERT4JIT_test_set.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX2\CPa_effectivenes_pre_vs_post_calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78406385-002D-49C9-BF57-A42D7B290FA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E6ADEE2-AAB1-4025-8B07-000CCCB8C364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OS_alpha_0.05" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="53">
   <si>
     <t>nr_instances</t>
   </si>
@@ -91,9 +91,6 @@
     <t>0.897069872</t>
   </si>
   <si>
-    <t>0.921111946</t>
-  </si>
-  <si>
     <t>0.900826446</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>0.917355372</t>
   </si>
   <si>
-    <t>0.889556724</t>
-  </si>
-  <si>
     <t>0.888805409</t>
   </si>
   <si>
@@ -136,33 +130,18 @@
     <t>0.947491249</t>
   </si>
   <si>
-    <t>0.949824971</t>
-  </si>
-  <si>
     <t>0.938545313</t>
   </si>
   <si>
-    <t>0.928043563</t>
-  </si>
-  <si>
-    <t>0.910151692</t>
-  </si>
-  <si>
     <t>0.895760405</t>
   </si>
   <si>
-    <t>0.900816803</t>
-  </si>
-  <si>
     <t>0.901983664</t>
   </si>
   <si>
     <t>0.899260988</t>
   </si>
   <si>
-    <t>0.914430183</t>
-  </si>
-  <si>
     <t>0.898872034</t>
   </si>
   <si>
@@ -175,9 +154,6 @@
     <t>0.849474912</t>
   </si>
   <si>
-    <t>0.836250486</t>
-  </si>
-  <si>
     <t>0.843640607</t>
   </si>
   <si>
@@ -206,13 +182,28 @@
   </si>
   <si>
     <t>StDEV</t>
+  </si>
+  <si>
+    <t>Precision_clean</t>
+  </si>
+  <si>
+    <t>recall_clean</t>
+  </si>
+  <si>
+    <t>Precision faulty</t>
+  </si>
+  <si>
+    <t>recall_faulty</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,10 +225,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -291,24 +297,37 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -538,14 +557,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="15" width="12" style="4" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -586,8 +605,20 @@
         <v>12</v>
       </c>
       <c r="P1" s="5"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1331</v>
       </c>
@@ -630,8 +661,23 @@
         <v>0.80309544282029233</v>
       </c>
       <c r="P2" s="4"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>I2/(I2+J2)</f>
+        <v>0.92201382033563672</v>
+      </c>
+      <c r="R2">
+        <f>I2/1152</f>
+        <v>0.81076388888888884</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>H2/11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1331</v>
       </c>
@@ -674,8 +720,23 @@
         <v>0.74634565778159934</v>
       </c>
       <c r="P3" s="4"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">I3/(I3+J3)</f>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">I3/1152</f>
+        <v>0.75347222222222221</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="4">H3/11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1331</v>
       </c>
@@ -718,8 +779,23 @@
         <v>0.83748925193465173</v>
       </c>
       <c r="P4" s="4"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.93834296724470134</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.84548611111111116</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1331</v>
       </c>
@@ -762,8 +838,23 @@
         <v>0.67497850386930347</v>
       </c>
       <c r="P5" s="4"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.94806763285024154</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.68142361111111116</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1331</v>
       </c>
@@ -806,8 +897,23 @@
         <v>0.71281169389509891</v>
       </c>
       <c r="P6" s="4"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.92625698324022343</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.71961805555555558</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1331</v>
       </c>
@@ -850,8 +956,23 @@
         <v>0.80567497850386927</v>
       </c>
       <c r="P7" s="4"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.9204322200392927</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.81336805555555558</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1331</v>
       </c>
@@ -894,8 +1015,24 @@
         <v>0.79363714531384355</v>
       </c>
       <c r="P8" s="4"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.92023928215353934</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.80121527777777779</v>
+      </c>
+      <c r="T8">
+        <f t="shared" ref="T8" si="5">H8/(H8+K8)</f>
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1331</v>
       </c>
@@ -938,8 +1075,23 @@
         <v>0.80395528804815131</v>
       </c>
       <c r="P9" s="4"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.949238578680203</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.81163194444444442</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1331</v>
       </c>
@@ -982,8 +1134,23 @@
         <v>0.85382631126397246</v>
       </c>
       <c r="P10" s="4"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.93590951932139488</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.86197916666666663</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1331</v>
       </c>
@@ -1026,8 +1193,23 @@
         <v>0.81771281169389509</v>
       </c>
       <c r="P11" s="4"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.93694581280788181</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.82552083333333337</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D12" s="6">
         <f>AVERAGE(D2:D11)</f>
         <v>978.7</v>
@@ -1044,6 +1226,14 @@
         <f>AVERAGE(I2:I11)</f>
         <v>912.9</v>
       </c>
+      <c r="J12" s="6">
+        <f>AVERAGE(J2:J11)</f>
+        <v>65.7</v>
+      </c>
+      <c r="K12" s="6">
+        <f>AVERAGE(K2:K11)</f>
+        <v>0.1</v>
+      </c>
       <c r="N12" s="6">
         <f>AVERAGE(N2:N11)</f>
         <v>0.93298635770162552</v>
@@ -1055,23 +1245,31 @@
       <c r="P12" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12" s="10">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.93307801500064469</v>
+      </c>
+      <c r="R12" s="10">
+        <f t="shared" si="6"/>
+        <v>0.7924479166666667</v>
+      </c>
+      <c r="T12" s="10">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0</v>
+      </c>
+      <c r="U12" s="10">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G13" s="6"/>
-      <c r="H13">
-        <f>H12+J13</f>
-        <v>65.7</v>
-      </c>
       <c r="I13">
-        <f>I12+K13</f>
-        <v>913</v>
-      </c>
-      <c r="J13" s="6">
-        <f>AVERAGE(J2:J11)</f>
-        <v>65.7</v>
-      </c>
-      <c r="K13" s="6">
-        <f>AVERAGE(K2:K11)</f>
+        <f>I12+J12</f>
+        <v>978.6</v>
+      </c>
+      <c r="K13">
+        <f>H12+K12</f>
         <v>0.1</v>
       </c>
       <c r="N13" s="4">
@@ -1083,12 +1281,12 @@
         <v>5.6333462236109556E-2</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1099,13 +1297,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91D9C8A4-BC01-4E36-A374-C0026584A26C}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="15" width="12" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1145,8 +1343,20 @@
       <c r="O1" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1331</v>
       </c>
@@ -1191,8 +1401,24 @@
         <v>0.96130696474634569</v>
       </c>
       <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>I2/(I2+J2)</f>
+        <v>0.89983844911147015</v>
+      </c>
+      <c r="R2">
+        <f>I2/1152</f>
+        <v>0.96701388888888884</v>
+      </c>
+      <c r="T2">
+        <f>H2/(H2+K2)</f>
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="U2">
+        <f>H2/11</f>
+        <v>0.36363636363636365</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1331</v>
       </c>
@@ -1224,7 +1450,7 @@
         <v>142</v>
       </c>
       <c r="K3" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
@@ -1237,8 +1463,23 @@
         <v>0.94496990541702497</v>
       </c>
       <c r="P3" s="2"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">I3/(I3+J3)</f>
+        <v>0.88557614826752618</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R9" si="3">I3/1152</f>
+        <v>0.95399305555555558</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="4">H3/11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>1331</v>
       </c>
@@ -1283,59 +1524,91 @@
         <v>0.96474634565778161</v>
       </c>
       <c r="P4" s="2"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.89528377298161466</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T11" si="5">H4/(H4+K4)</f>
+        <v>0.25</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="4"/>
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>1331</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1170</v>
-      </c>
-      <c r="E5" s="2">
-        <v>161</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1065</v>
-      </c>
-      <c r="G5" s="2">
-        <v>105</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>1065</v>
-      </c>
-      <c r="J5" s="2">
-        <v>105</v>
-      </c>
-      <c r="K5" s="2">
-        <v>0</v>
+      <c r="B5">
+        <v>0.88955672426746812</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>1268</v>
+      </c>
+      <c r="E5">
+        <v>63</v>
+      </c>
+      <c r="F5">
+        <v>1121</v>
+      </c>
+      <c r="G5">
+        <v>147</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>1115</v>
+      </c>
+      <c r="J5">
+        <v>144</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>0.91025641025641024</v>
+        <v>0.88406940063091488</v>
       </c>
       <c r="O5" s="4">
         <f t="shared" si="1"/>
-        <v>0.91573516766981944</v>
+        <v>0.96388650042992263</v>
       </c>
       <c r="P5" s="2"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.88562351072279588</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.96788194444444442</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="5"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>0.54545454545454541</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>1331</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -1362,7 +1635,7 @@
         <v>132</v>
       </c>
       <c r="K6" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -1375,13 +1648,28 @@
         <v>0.95012897678417885</v>
       </c>
       <c r="P6" s="2"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.8932902182700081</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.95920138888888884</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>1331</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
@@ -1421,13 +1709,29 @@
         <v>0.95786758383490966</v>
       </c>
       <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.891653290529695</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.96440972222222221</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>1331</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2">
         <v>0</v>
@@ -1467,13 +1771,29 @@
         <v>0.9217540842648323</v>
       </c>
       <c r="P8" s="2"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.89548494983277593</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.9296875</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="5"/>
+        <v>0.5</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>1331</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2">
         <v>0</v>
@@ -1513,59 +1833,91 @@
         <v>0.96044711951848671</v>
       </c>
       <c r="P9" s="2"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.91109298531810767</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.96961805555555558</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>1331</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1320</v>
-      </c>
-      <c r="E10" s="2">
-        <v>11</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1161</v>
-      </c>
-      <c r="G10" s="2">
-        <v>147</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1172</v>
-      </c>
-      <c r="J10" s="2">
-        <v>147</v>
-      </c>
-      <c r="K10" s="2">
-        <v>0</v>
+      <c r="B10">
+        <v>0.89030803906836964</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>1280</v>
+      </c>
+      <c r="E10">
+        <v>51</v>
+      </c>
+      <c r="F10">
+        <v>1134</v>
+      </c>
+      <c r="G10">
+        <v>146</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <v>1131</v>
+      </c>
+      <c r="J10">
+        <v>141</v>
+      </c>
+      <c r="K10">
+        <v>5</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
-        <v>0.87954545454545452</v>
+        <v>0.88593750000000004</v>
       </c>
       <c r="O10" s="4">
         <f>F10/1163</f>
-        <v>0.99828030954428204</v>
+        <v>0.97506448839208948</v>
       </c>
       <c r="P10" s="2"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.88915094339622647</v>
+      </c>
+      <c r="R10">
+        <f>I10/1172</f>
+        <v>0.96501706484641636</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="5"/>
+        <v>0.375</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>1331</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
@@ -1592,7 +1944,7 @@
         <v>148</v>
       </c>
       <c r="K11" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -1605,64 +1957,96 @@
         <v>0.99742046431642306</v>
       </c>
       <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.88685015290519875</v>
+      </c>
+      <c r="R11">
+        <f>I11/1172</f>
+        <v>0.98976109215017061</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D12" s="6">
         <f>AVERAGE(D2:D11)</f>
-        <v>1246.3</v>
+        <v>1252.0999999999999</v>
       </c>
       <c r="F12" s="6">
         <f>AVERAGE(F2:F11)</f>
-        <v>1113.3</v>
+        <v>1116.2</v>
       </c>
       <c r="H12" s="6">
         <f>AVERAGE(H2:H11)</f>
-        <v>1.1000000000000001</v>
+        <v>1.9</v>
       </c>
       <c r="I12" s="6">
         <f>AVERAGE(I2:I11)</f>
-        <v>1113.4000000000001</v>
+        <v>1114.3</v>
+      </c>
+      <c r="J12" s="6">
+        <f>AVERAGE(J2:J11)</f>
+        <v>133.1</v>
+      </c>
+      <c r="K12" s="6">
+        <f>AVERAGE(K2:K11)</f>
+        <v>4.5999999999999996</v>
       </c>
       <c r="N12" s="6">
         <f>AVERAGE(N2:N11)</f>
-        <v>0.8935338429076225</v>
+        <v>0.89155434649052745</v>
       </c>
       <c r="O12" s="6">
         <f>AVERAGE(O2:O11)</f>
-        <v>0.95726569217540847</v>
+        <v>0.95975924333619955</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12" s="10">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.89338444213354185</v>
+      </c>
+      <c r="R12" s="10">
+        <f t="shared" si="6"/>
+        <v>0.96388059347743638</v>
+      </c>
+      <c r="T12" s="10">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.25993589743589746</v>
+      </c>
+      <c r="U12" s="12">
+        <f t="shared" si="7"/>
+        <v>0.1727272727272727</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G13" s="6"/>
-      <c r="H13">
-        <f>H12+J13</f>
-        <v>130.9</v>
-      </c>
       <c r="I13">
-        <f>I12+K13</f>
-        <v>1115.4000000000001</v>
-      </c>
-      <c r="J13" s="6">
-        <f>AVERAGE(J2:J11)</f>
-        <v>129.80000000000001</v>
-      </c>
-      <c r="K13" s="6">
-        <f>AVERAGE(K2:K11)</f>
-        <v>2</v>
+        <f>I12+J12</f>
+        <v>1247.3999999999999</v>
+      </c>
+      <c r="K13">
+        <f>H12+K12</f>
+        <v>6.5</v>
       </c>
       <c r="N13" s="4">
         <f>STDEV(N2:N11)</f>
-        <v>9.9303438073514091E-3</v>
+        <v>7.6032326312974923E-3</v>
       </c>
       <c r="O13" s="4">
         <f>STDEV(O2:O11)</f>
-        <v>2.7008966038714298E-2</v>
+        <v>1.9598268601221224E-2</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1672,13 +2056,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{787CC0FA-8078-46A2-9C4D-56D698E2D65C}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="15" width="12" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1718,54 +2102,82 @@
       <c r="O1" s="4" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1331</v>
       </c>
       <c r="B2">
-        <v>0.86927122464312545</v>
+        <v>0.83921863260706231</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="D2">
-        <v>1315</v>
+        <v>1243</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>1157</v>
+        <v>1117</v>
       </c>
       <c r="G2">
-        <v>158</v>
+        <v>126</v>
       </c>
       <c r="H2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>1141</v>
+        <v>1115</v>
       </c>
       <c r="J2">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="K2">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="4">
         <f>F2/D2</f>
-        <v>0.8798479087452471</v>
+        <v>0.89863234111021717</v>
       </c>
       <c r="O2" s="4">
         <f>F2/1163</f>
-        <v>0.99484092863284612</v>
+        <v>0.96044711951848671</v>
       </c>
       <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>I2/(I2+J2)</f>
+        <v>0.90064620355411951</v>
+      </c>
+      <c r="R2">
+        <f>I2/1152</f>
+        <v>0.96788194444444442</v>
+      </c>
+      <c r="T2">
+        <f>H2/(H2+K2)</f>
+        <v>0.4</v>
+      </c>
+      <c r="U2">
+        <f>H2/16</f>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1331</v>
       </c>
@@ -1797,7 +2209,7 @@
         <v>161</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
@@ -1810,8 +2222,23 @@
         <v>0.96818572656921753</v>
       </c>
       <c r="P3" s="2"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">I3/(I3+J3)</f>
+        <v>0.87490287490287488</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">I3/1152</f>
+        <v>0.97743055555555558</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="4">H3/11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1331</v>
       </c>
@@ -1856,8 +2283,24 @@
         <v>0.96732588134135855</v>
       </c>
       <c r="P4" s="2"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.89482071713147415</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.97482638888888884</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T11" si="5">H4/(H4+K4)</f>
+        <v>0.25</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="4"/>
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1331</v>
       </c>
@@ -1902,8 +2345,24 @@
         <v>0.98194325021496132</v>
       </c>
       <c r="P5" s="2"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.88395638629283491</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.98524305555555558</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="5"/>
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>0.63636363636363635</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1331</v>
       </c>
@@ -1935,7 +2394,7 @@
         <v>143</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
@@ -1948,8 +2407,24 @@
         <v>0.97248495270851243</v>
       </c>
       <c r="P6" s="2"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.88757861635220126</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.98003472222222221</v>
+      </c>
+      <c r="T6">
+        <f>H6/(H6+K6)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1331</v>
       </c>
@@ -1994,8 +2469,24 @@
         <v>0.97162510748065345</v>
       </c>
       <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.88722397476340698</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.9765625</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="5"/>
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>0.45454545454545453</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1331</v>
       </c>
@@ -2040,8 +2531,24 @@
         <v>0.99226139294926918</v>
       </c>
       <c r="P8" s="2"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.88366718027734981</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.99565972222222221</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="5"/>
+        <v>0.30434782608695654</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>0.63636363636363635</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1331</v>
       </c>
@@ -2086,8 +2593,24 @@
         <v>0.99140154772141009</v>
       </c>
       <c r="P9" s="2"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.90125391849529779</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.99826388888888884</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1331</v>
       </c>
@@ -2119,7 +2642,7 @@
         <v>112</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2132,110 +2655,157 @@
         <v>0.96474634565778161</v>
       </c>
       <c r="P10" s="2"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.90923824959481359</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.97395833333333337</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1331</v>
       </c>
       <c r="B11">
-        <v>0.84898572501878289</v>
+        <v>0.8422238918106687</v>
       </c>
       <c r="C11">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="D11">
-        <v>1252</v>
+        <v>1277</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>1130</v>
+        <v>1121</v>
       </c>
       <c r="G11">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I11">
-        <v>1130</v>
+        <v>1115</v>
       </c>
       <c r="J11">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="4">
         <f t="shared" si="0"/>
-        <v>0.902555910543131</v>
+        <v>0.8778386844166014</v>
       </c>
       <c r="O11" s="4">
         <f t="shared" si="1"/>
-        <v>0.97162510748065345</v>
+        <v>0.96388650042992263</v>
       </c>
       <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.882120253164557</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.96788194444444442</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="5"/>
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>0.54545454545454541</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D12" s="6">
         <f>AVERAGE(D2:D11)</f>
-        <v>1282.5999999999999</v>
+        <v>1277.9000000000001</v>
       </c>
       <c r="F12" s="6">
         <f>AVERAGE(F2:F11)</f>
-        <v>1137</v>
+        <v>1132.0999999999999</v>
       </c>
       <c r="H12" s="6">
         <f>AVERAGE(H2:H11)</f>
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="I12" s="6">
         <f>AVERAGE(I2:I11)</f>
-        <v>1132.8</v>
+        <v>1128.7</v>
+      </c>
+      <c r="J12" s="6">
+        <f>AVERAGE(J2:J11)</f>
+        <v>138.9</v>
+      </c>
+      <c r="K12" s="6">
+        <f>AVERAGE(K2:K11)</f>
+        <v>9.5</v>
       </c>
       <c r="N12" s="6">
         <f>AVERAGE(N2:N11)</f>
-        <v>0.88670924300801057</v>
+        <v>0.88611596363185474</v>
       </c>
       <c r="O12" s="6">
         <f>AVERAGE(O2:O11)</f>
-        <v>0.97764402407566631</v>
+        <v>0.97343078245915726</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12" s="10">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.89054083745289303</v>
+      </c>
+      <c r="R12" s="10">
+        <f t="shared" si="6"/>
+        <v>0.97977430555555567</v>
+      </c>
+      <c r="T12" s="10">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.26810751217797696</v>
+      </c>
+      <c r="U12" s="10">
+        <f t="shared" si="7"/>
+        <v>0.30340909090909085</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G13" s="6"/>
-      <c r="H13">
-        <f>H12+J13</f>
-        <v>141.69999999999999</v>
-      </c>
       <c r="I13">
-        <f>I12+K13</f>
-        <v>1140.8999999999999</v>
-      </c>
-      <c r="J13" s="6">
-        <f>AVERAGE(J2:J11)</f>
-        <v>137.5</v>
-      </c>
-      <c r="K13" s="6">
-        <f>AVERAGE(K2:K11)</f>
-        <v>8.1</v>
+        <f>I12+J12</f>
+        <v>1267.6000000000001</v>
+      </c>
+      <c r="K13">
+        <f>H12+K12</f>
+        <v>12.9</v>
       </c>
       <c r="N13" s="4">
         <f>STDEV(N2:N11)</f>
-        <v>1.3171665096682083E-2</v>
+        <v>1.2826047052060861E-2</v>
       </c>
       <c r="O13" s="4">
         <f>STDEV(O2:O11)</f>
-        <v>1.1443086716925854E-2</v>
+        <v>1.1323653479893813E-2</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2245,14 +2815,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2FCA70D0-21F4-430E-BD4B-E7F2FD2567A7}">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="14" width="12" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2292,13 +2862,25 @@
       <c r="O1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>2571</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -2325,7 +2907,7 @@
         <v>103</v>
       </c>
       <c r="K2" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
@@ -2338,15 +2920,28 @@
         <v>0.89890939597315433</v>
       </c>
       <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>I2/(I2+J2)</f>
+        <v>0.95414069456812112</v>
+      </c>
+      <c r="R2">
+        <f>I2/2374</f>
+        <v>0.90269587194608258</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>H2/11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2571</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2">
         <v>0</v>
@@ -2373,7 +2968,7 @@
         <v>132</v>
       </c>
       <c r="K3" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
@@ -2386,15 +2981,28 @@
         <v>0.96182885906040272</v>
       </c>
       <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">I3/(I3+J3)</f>
+        <v>0.94556701030927837</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">I3/2374</f>
+        <v>0.96588037068239263</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="4">H3/11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2571</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
@@ -2421,7 +3029,7 @@
         <v>142</v>
       </c>
       <c r="K4" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
@@ -2434,15 +3042,28 @@
         <v>0.94043624161073824</v>
       </c>
       <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.94043624161073824</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.94439764111204716</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2571</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="2">
         <v>0</v>
@@ -2482,15 +3103,29 @@
         <v>0.97021812080536918</v>
       </c>
       <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.94062627084180561</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.97430497051390064</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T6" si="5">H5/(H5+K5)</f>
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2571</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -2530,15 +3165,29 @@
         <v>0.94924496644295298</v>
       </c>
       <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.94915966386554618</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.95155855096882902</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="5"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>0.36363636363636365</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2571</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
@@ -2565,7 +3214,7 @@
         <v>115</v>
       </c>
       <c r="K7" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -2578,15 +3227,28 @@
         <v>0.94253355704697983</v>
       </c>
       <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.95131244707874685</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.94650379106992422</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2571</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2">
         <v>0</v>
@@ -2613,7 +3275,7 @@
         <v>114</v>
       </c>
       <c r="K8" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -2626,15 +3288,28 @@
         <v>0.91317114093959728</v>
       </c>
       <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.95024006983849851</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.91701769165964619</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2571</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2">
         <v>0</v>
@@ -2661,7 +3336,7 @@
         <v>135</v>
       </c>
       <c r="K9" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -2674,63 +3349,90 @@
         <v>0.92701342281879195</v>
       </c>
       <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.94243070362473347</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.93091828138163435</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>2571</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0</v>
-      </c>
-      <c r="D10" s="2">
-        <v>2328</v>
-      </c>
-      <c r="E10" s="2">
-        <v>243</v>
-      </c>
-      <c r="F10" s="2">
-        <v>2199</v>
-      </c>
-      <c r="G10" s="2">
-        <v>129</v>
-      </c>
-      <c r="H10" s="2">
-        <v>0</v>
-      </c>
-      <c r="I10" s="2">
-        <v>2199</v>
-      </c>
-      <c r="J10" s="2">
-        <v>129</v>
-      </c>
-      <c r="K10" s="2">
-        <v>0</v>
+      <c r="B10">
+        <v>0.94749124854142353</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>2383</v>
+      </c>
+      <c r="E10">
+        <v>188</v>
+      </c>
+      <c r="F10">
+        <v>2248</v>
+      </c>
+      <c r="G10">
+        <v>135</v>
+      </c>
+      <c r="H10">
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <v>2245</v>
+      </c>
+      <c r="J10">
+        <v>135</v>
+      </c>
+      <c r="K10">
+        <v>1</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
-        <v>0.94458762886597936</v>
+        <v>0.94334872010071336</v>
       </c>
       <c r="O10" s="2">
         <f t="shared" si="1"/>
-        <v>0.9223993288590604</v>
+        <v>0.94295302013422821</v>
       </c>
       <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.94327731092436973</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.94566133108677342</v>
+      </c>
+      <c r="T10">
+        <f t="shared" ref="T10" si="6">H10/(H10+K10)</f>
+        <v>0.75</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>2571</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
@@ -2757,7 +3459,7 @@
         <v>158</v>
       </c>
       <c r="K11" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -2770,71 +3472,100 @@
         <v>0.96476510067114096</v>
       </c>
       <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.93572009764035802</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.96882898062342038</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D12" s="6">
         <f>AVERAGE(D2:D11)</f>
-        <v>2368.6</v>
+        <v>2374.1</v>
       </c>
       <c r="F12" s="6">
         <f>AVERAGE(F2:F11)</f>
-        <v>2238.6999999999998</v>
+        <v>2243.6</v>
       </c>
       <c r="H12" s="6">
         <f>AVERAGE(H2:H11)</f>
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="I12" s="6">
         <f>AVERAGE(I2:I11)</f>
-        <v>2238.3000000000002</v>
+        <v>2242.9</v>
+      </c>
+      <c r="J12" s="6">
+        <f>AVERAGE(J2:J11)</f>
+        <v>130.1</v>
+      </c>
+      <c r="K12" s="6">
+        <f>AVERAGE(K2:K11)</f>
+        <v>3.8</v>
       </c>
       <c r="N12" s="6">
         <f>AVERAGE(N2:N11)</f>
-        <v>0.94527307440274266</v>
+        <v>0.94514918352621602</v>
       </c>
       <c r="O12" s="6">
         <f>AVERAGE(O2:O11)</f>
-        <v>0.93905201342281885</v>
+        <v>0.94110738255033566</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="Q12" s="10">
+        <f t="shared" ref="Q12:R12" si="7">AVERAGE(Q2:Q11)</f>
+        <v>0.9452910510302196</v>
+      </c>
+      <c r="R12" s="10">
+        <f t="shared" si="7"/>
+        <v>0.94477674810446499</v>
+      </c>
+      <c r="T12" s="10">
+        <f t="shared" ref="T12:U12" si="8">AVERAGE(T2:T11)</f>
+        <v>0.13214285714285715</v>
+      </c>
+      <c r="U12" s="10">
+        <f t="shared" si="8"/>
+        <v>6.363636363636363E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G13" s="6"/>
-      <c r="H13">
-        <f>H12+J13</f>
-        <v>129.9</v>
-      </c>
       <c r="I13">
-        <f>I12+K13</f>
-        <v>2238.7000000000003</v>
-      </c>
-      <c r="J13" s="6">
-        <f>AVERAGE(J2:J11)</f>
-        <v>129.5</v>
-      </c>
-      <c r="K13" s="6">
-        <f>AVERAGE(K2:K11)</f>
-        <v>0.4</v>
+        <f>I12+J12</f>
+        <v>2373</v>
+      </c>
+      <c r="K13">
+        <f>H12+K12</f>
+        <v>4.5</v>
       </c>
       <c r="N13" s="4">
         <f>STDEV(N2:N11)</f>
-        <v>5.7356980084378477E-3</v>
+        <v>5.7654516947357858E-3</v>
       </c>
       <c r="O13" s="4">
         <f>STDEV(O2:O11)</f>
-        <v>2.350578224486459E-2</v>
+        <v>2.2775124632335796E-2</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>54</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2844,14 +3575,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D608BFA9-BFE5-4B6B-B3E9-B010CC376E9F}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="14" width="12" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2891,105 +3622,149 @@
       <c r="O1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>2571</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="2">
-        <v>30</v>
-      </c>
-      <c r="D2" s="2">
-        <v>2541</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>2383</v>
-      </c>
-      <c r="G2" s="2">
-        <v>155</v>
-      </c>
-      <c r="H2" s="2">
-        <v>4</v>
-      </c>
-      <c r="I2" s="2">
-        <v>2382</v>
-      </c>
-      <c r="J2" s="2">
-        <v>153</v>
-      </c>
-      <c r="K2" s="2">
-        <v>2</v>
+      <c r="B2">
+        <v>0.91170750680668999</v>
+      </c>
+      <c r="C2">
+        <v>59</v>
+      </c>
+      <c r="D2">
+        <v>2512</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>2344</v>
+      </c>
+      <c r="G2">
+        <v>168</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
+        <v>2338</v>
+      </c>
+      <c r="J2">
+        <v>158</v>
+      </c>
+      <c r="K2">
+        <v>10</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="4">
         <f>F2/D2</f>
-        <v>0.93781975600157419</v>
+        <v>0.93312101910828027</v>
       </c>
       <c r="O2" s="2">
         <f>F2/2384</f>
-        <v>0.99958053691275173</v>
+        <v>0.98322147651006708</v>
       </c>
       <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>I2/(I2+J2)</f>
+        <v>0.93669871794871795</v>
+      </c>
+      <c r="R2">
+        <f>I2/2374</f>
+        <v>0.98483572030328559</v>
+      </c>
+      <c r="T2">
+        <f>H2/(H2+K2)</f>
+        <v>0.375</v>
+      </c>
+      <c r="U2">
+        <f>H2/11</f>
+        <v>0.54545454545454541</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2571</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="2">
-        <v>88</v>
-      </c>
-      <c r="D3" s="2">
-        <v>2483</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2">
-        <v>2340</v>
-      </c>
-      <c r="G3" s="2">
-        <v>143</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0</v>
-      </c>
-      <c r="I3" s="2">
-        <v>2340</v>
-      </c>
-      <c r="J3" s="2">
-        <v>143</v>
-      </c>
-      <c r="K3" s="2">
-        <v>0</v>
+      <c r="B3">
+        <v>0.89926098794243481</v>
+      </c>
+      <c r="C3">
+        <v>102</v>
+      </c>
+      <c r="D3">
+        <v>2469</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>2312</v>
+      </c>
+      <c r="G3">
+        <v>157</v>
+      </c>
+      <c r="H3">
+        <v>2</v>
+      </c>
+      <c r="I3">
+        <v>2310</v>
+      </c>
+      <c r="J3">
+        <v>155</v>
+      </c>
+      <c r="K3">
+        <v>2</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="4">
         <f t="shared" ref="N3:N11" si="0">F3/D3</f>
-        <v>0.94240837696335078</v>
+        <v>0.93641150263264483</v>
       </c>
       <c r="O3" s="2">
         <f t="shared" ref="O3:O11" si="1">F3/2384</f>
-        <v>0.98154362416107388</v>
+        <v>0.96979865771812079</v>
       </c>
       <c r="P3" s="2"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">I3/(I3+J3)</f>
+        <v>0.93711967545638941</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">I3/2374</f>
+        <v>0.97304128053917438</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T10" si="4">H3/(H3+K3)</f>
+        <v>0.5</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">H3/11</f>
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2571</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2">
         <v>104</v>
@@ -3029,59 +3804,90 @@
         <v>0.96602348993288589</v>
       </c>
       <c r="P4" s="2"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.93352249695987033</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.97009267059814663</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2571</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="2">
-        <v>108</v>
-      </c>
-      <c r="D5" s="2">
-        <v>2463</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
-      </c>
-      <c r="F5" s="2">
-        <v>2316</v>
-      </c>
-      <c r="G5" s="2">
-        <v>147</v>
-      </c>
-      <c r="H5" s="2">
-        <v>0</v>
-      </c>
-      <c r="I5" s="2">
-        <v>2316</v>
-      </c>
-      <c r="J5" s="2">
-        <v>146</v>
-      </c>
-      <c r="K5" s="2">
-        <v>1</v>
+      <c r="B5">
+        <v>0.90042784908595874</v>
+      </c>
+      <c r="C5">
+        <v>91</v>
+      </c>
+      <c r="D5">
+        <v>2480</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>2315</v>
+      </c>
+      <c r="G5">
+        <v>165</v>
+      </c>
+      <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>2309</v>
+      </c>
+      <c r="J5">
+        <v>156</v>
+      </c>
+      <c r="K5">
+        <v>9</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="4">
         <f t="shared" si="0"/>
-        <v>0.94031668696711324</v>
+        <v>0.93346774193548387</v>
       </c>
       <c r="O5" s="2">
         <f t="shared" si="1"/>
-        <v>0.97147651006711411</v>
+        <v>0.97105704697986572</v>
       </c>
       <c r="P5" s="2"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.93671399594320481</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.97262005054759904</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.4</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.54545454545454541</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2571</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2">
         <v>109</v>
@@ -3121,13 +3927,29 @@
         <v>0.97273489932885904</v>
       </c>
       <c r="P6" s="2"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.94410444716442266</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.97472620050547598</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.45454545454545453</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2571</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2">
         <v>130</v>
@@ -3167,59 +3989,90 @@
         <v>0.96979865771812079</v>
       </c>
       <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.94715280622695619</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.97388374052232518</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2571</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="2">
-        <v>82</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2489</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2">
-        <v>2351</v>
-      </c>
-      <c r="G8" s="2">
-        <v>138</v>
-      </c>
-      <c r="H8" s="2">
-        <v>0</v>
-      </c>
-      <c r="I8" s="2">
-        <v>2351</v>
-      </c>
-      <c r="J8" s="2">
-        <v>138</v>
-      </c>
-      <c r="K8" s="2">
-        <v>0</v>
+      <c r="B8">
+        <v>0.90509529366005448</v>
+      </c>
+      <c r="C8">
+        <v>98</v>
+      </c>
+      <c r="D8">
+        <v>2473</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>2327</v>
+      </c>
+      <c r="G8">
+        <v>146</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
+        <v>2326</v>
+      </c>
+      <c r="J8">
+        <v>144</v>
+      </c>
+      <c r="K8">
+        <v>3</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="4">
         <f t="shared" si="0"/>
-        <v>0.94455604660506232</v>
+        <v>0.94096239385361913</v>
       </c>
       <c r="O8" s="2">
         <f t="shared" si="1"/>
-        <v>0.98615771812080533</v>
+        <v>0.97609060402684567</v>
       </c>
       <c r="P8" s="2"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.94170040485829964</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.97978096040438079</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.4</v>
+      </c>
+      <c r="U8">
+        <f>H8/11</f>
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2571</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C9" s="2">
         <v>88</v>
@@ -3259,13 +4112,29 @@
         <v>0.96937919463087252</v>
       </c>
       <c r="P9" s="2"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.93214862681744748</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.97219882055602358</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>2571</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C10" s="2">
         <v>115</v>
@@ -3283,7 +4152,7 @@
         <v>153</v>
       </c>
       <c r="H10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="2">
         <v>2302</v>
@@ -3305,13 +4174,28 @@
         <v>0.96602348993288589</v>
       </c>
       <c r="P10" s="2"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.93767820773930755</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.96967144060657118</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>2571</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2">
         <v>177</v>
@@ -3351,64 +4235,95 @@
         <v>0.94295302013422821</v>
       </c>
       <c r="P11" s="2"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.93901420217209686</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.94692502106149956</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D12" s="6">
         <f>AVERAGE(D2:D11)</f>
-        <v>2467.9</v>
+        <v>2463.6999999999998</v>
       </c>
       <c r="F12" s="6">
         <f>AVERAGE(F2:F11)</f>
-        <v>2318.6</v>
+        <v>2309.4</v>
       </c>
       <c r="H12" s="6">
         <f>AVERAGE(H2:H11)</f>
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="I12" s="6">
         <f>AVERAGE(I2:I11)</f>
-        <v>2317.6</v>
+        <v>2307</v>
+      </c>
+      <c r="J12" s="6">
+        <f>AVERAGE(J2:J11)</f>
+        <v>151</v>
+      </c>
+      <c r="K12" s="6">
+        <f>AVERAGE(K2:K11)</f>
+        <v>3.4</v>
       </c>
       <c r="N12" s="6">
         <f>AVERAGE(N2:N11)</f>
-        <v>0.93951400524010287</v>
+        <v>0.93740018433939554</v>
       </c>
       <c r="O12" s="6">
         <f>AVERAGE(O2:O11)</f>
-        <v>0.97256711409395957</v>
+        <v>0.96870805369127511</v>
       </c>
       <c r="P12" s="7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12" s="10">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.93858535812867117</v>
+      </c>
+      <c r="R12" s="10">
+        <f t="shared" si="6"/>
+        <v>0.97177759056444812</v>
+      </c>
+      <c r="T12" s="10">
+        <f>AVERAGE(T2:T11)</f>
+        <v>0.25581168831168827</v>
+      </c>
+      <c r="U12" s="10">
+        <f t="shared" ref="U12" si="7">AVERAGE(U2:U11)</f>
+        <v>0.21818181818181817</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G13" s="6"/>
-      <c r="H13">
-        <f>H12+J13</f>
-        <v>149</v>
-      </c>
       <c r="I13">
-        <f>I12+K13</f>
-        <v>2318.9</v>
-      </c>
-      <c r="J13" s="6">
-        <f>AVERAGE(J2:J11)</f>
-        <v>147.69999999999999</v>
-      </c>
-      <c r="K13" s="6">
-        <f>AVERAGE(K2:K11)</f>
-        <v>1.3</v>
+        <f>I12+J12</f>
+        <v>2458</v>
+      </c>
+      <c r="K13">
+        <f>H12+K12</f>
+        <v>5.8</v>
       </c>
       <c r="N13" s="4">
         <f>STDEV(N2:N11)</f>
-        <v>4.9220971621303572E-3</v>
+        <v>5.0021945479345855E-3</v>
       </c>
       <c r="O13" s="4">
         <f>STDEV(O2:O11)</f>
-        <v>1.4819973792154838E-2</v>
+        <v>1.0367896656672194E-2</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -3418,14 +4333,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A8D7D0-012F-49AC-A6AE-75C7FB20B858}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="14" max="14" width="10" style="4" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3465,13 +4381,25 @@
       <c r="O1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>2571</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C2" s="2">
         <v>194</v>
@@ -3498,7 +4426,7 @@
         <v>122</v>
       </c>
       <c r="K2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="4">
         <f>F2/D2</f>
@@ -3508,13 +4436,29 @@
         <f>F2/2384</f>
         <v>0.94588926174496646</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P2" s="2"/>
+      <c r="Q2">
+        <f>I2/(I2+J2)</f>
+        <v>0.94867480016827932</v>
+      </c>
+      <c r="R2">
+        <f>I2/2374</f>
+        <v>0.94987363100252742</v>
+      </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>H2/11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2571</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2">
         <v>276</v>
@@ -3541,7 +4485,7 @@
         <v>111</v>
       </c>
       <c r="K3" s="2">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N3" s="4">
         <f t="shared" ref="N3:N11" si="0">F3/D3</f>
@@ -3551,56 +4495,89 @@
         <f t="shared" ref="O3:O11" si="1">F3/2384</f>
         <v>0.91610738255033553</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P3" s="2"/>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">I3/(I3+J3)</f>
+        <v>0.95163398692810452</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">I3/2374</f>
+        <v>0.91996630160067394</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="4">H3/11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2571</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="2">
-        <v>306</v>
-      </c>
-      <c r="D4" s="2">
-        <v>2265</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2">
-        <v>2150</v>
-      </c>
-      <c r="G4" s="2">
-        <v>115</v>
-      </c>
-      <c r="H4" s="2">
-        <v>0</v>
-      </c>
-      <c r="I4" s="2">
-        <v>2150</v>
-      </c>
-      <c r="J4" s="2">
-        <v>115</v>
-      </c>
-      <c r="K4" s="2">
-        <v>0</v>
+      <c r="B4">
+        <v>0.84675223600000005</v>
+      </c>
+      <c r="C4">
+        <v>275</v>
+      </c>
+      <c r="D4">
+        <v>2296</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>2177</v>
+      </c>
+      <c r="G4">
+        <v>119</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>2175</v>
+      </c>
+      <c r="J4">
+        <v>119</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
       </c>
       <c r="N4" s="4">
         <f t="shared" si="0"/>
-        <v>0.94922737306843263</v>
+        <v>0.94817073170731703</v>
       </c>
       <c r="O4" s="2">
         <f t="shared" si="1"/>
-        <v>0.90184563758389258</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>0.91317114093959728</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.94812554489973844</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.91617523167649539</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T10" si="5">H4/(H4+K4)</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="4"/>
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>2571</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C5" s="2">
         <v>286</v>
@@ -3637,13 +4614,29 @@
         <f t="shared" si="1"/>
         <v>0.90981543624161076</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P5" s="2"/>
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.94923413566739601</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.91364785172704299</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>2571</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2">
         <v>284</v>
@@ -3661,7 +4654,7 @@
         <v>106</v>
       </c>
       <c r="H6" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I6" s="2">
         <v>2178</v>
@@ -3670,7 +4663,7 @@
         <v>105</v>
       </c>
       <c r="K6" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" s="4">
         <f t="shared" si="0"/>
@@ -3680,13 +4673,30 @@
         <f t="shared" si="1"/>
         <v>0.9148489932885906</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P6" s="2"/>
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.95400788436268069</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.91743892165122154</v>
+      </c>
+      <c r="T6">
+        <f>H6/(H6+K6)</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="4"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>2571</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2">
         <v>275</v>
@@ -3723,13 +4733,29 @@
         <f t="shared" si="1"/>
         <v>0.91988255033557043</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P7" s="2"/>
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.95513937282229966</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.9237573715248526</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>2571</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2">
         <v>256</v>
@@ -3747,7 +4773,7 @@
         <v>118</v>
       </c>
       <c r="H8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" s="2">
         <v>2197</v>
@@ -3756,7 +4782,7 @@
         <v>118</v>
       </c>
       <c r="K8" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N8" s="4">
         <f t="shared" si="0"/>
@@ -3766,13 +4792,30 @@
         <f t="shared" si="1"/>
         <v>0.92156040268456374</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P8" s="2"/>
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.94902807775377973</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.9254422914911542</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="5"/>
+        <v>0.25</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="4"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>2571</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="C9" s="2">
         <v>252</v>
@@ -3809,13 +4852,29 @@
         <f t="shared" si="1"/>
         <v>0.9186241610738255</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P9" s="2"/>
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.94437257438551103</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.92249368155012634</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>2571</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C10" s="2">
         <v>290</v>
@@ -3833,7 +4892,7 @@
         <v>120</v>
       </c>
       <c r="H10" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="2">
         <v>2161</v>
@@ -3842,7 +4901,7 @@
         <v>120</v>
       </c>
       <c r="K10" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" s="4">
         <f t="shared" si="0"/>
@@ -3852,13 +4911,30 @@
         <f t="shared" si="1"/>
         <v>0.90645973154362414</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P10" s="2"/>
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.94739149495835162</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.91027801179443979</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="4"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>2571</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2">
         <v>339</v>
@@ -3895,64 +4971,101 @@
         <f t="shared" si="1"/>
         <v>0.88968120805369133</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="P11" s="2"/>
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.95026881720430112</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.89342881213142378</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="D12" s="6">
         <f>AVERAGE(D2:D11)</f>
-        <v>2295.1999999999998</v>
+        <v>2298.3000000000002</v>
       </c>
       <c r="F12" s="6">
         <f>AVERAGE(F2:F11)</f>
-        <v>2180.1</v>
+        <v>2182.8000000000002</v>
       </c>
       <c r="H12" s="6">
         <f>AVERAGE(H2:H11)</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I12" s="6">
         <f>AVERAGE(I2:I11)</f>
-        <v>2179.8000000000002</v>
+        <v>2182.3000000000002</v>
+      </c>
+      <c r="J12" s="6">
+        <f>AVERAGE(J2:J11)</f>
+        <v>115.4</v>
+      </c>
+      <c r="K12" s="6">
+        <f>AVERAGE(K2:K11)</f>
+        <v>2</v>
       </c>
       <c r="N12" s="6">
         <f>AVERAGE(N2:N11)</f>
-        <v>0.94986217042288668</v>
+        <v>0.94975650628677522</v>
       </c>
       <c r="O12" s="6">
         <f>AVERAGE(O2:O11)</f>
-        <v>0.91447147651006711</v>
-      </c>
-      <c r="P12" s="7" t="s">
+        <v>0.91560402684563758</v>
+      </c>
+      <c r="P12" s="10" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q12" s="10">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.94978766891504429</v>
+      </c>
+      <c r="R12" s="10">
+        <f t="shared" si="6"/>
+        <v>0.91925021061499579</v>
+      </c>
+      <c r="T12" s="10">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.15833333333333333</v>
+      </c>
+      <c r="U12" s="10">
+        <f t="shared" si="7"/>
+        <v>4.5454545454545456E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="G13" s="6"/>
-      <c r="H13">
-        <f>H12+J13</f>
-        <v>115.3</v>
-      </c>
       <c r="I13">
-        <f>I12+K13</f>
-        <v>2179.9</v>
-      </c>
-      <c r="J13" s="6">
-        <f>AVERAGE(J2:J11)</f>
-        <v>115</v>
-      </c>
-      <c r="K13" s="6">
-        <f>AVERAGE(K2:K11)</f>
-        <v>0.1</v>
+        <f>I12+J12</f>
+        <v>2297.7000000000003</v>
+      </c>
+      <c r="K13">
+        <f>H12+K12</f>
+        <v>2.5</v>
       </c>
       <c r="N13" s="4">
         <f>STDEV(N2:N11)</f>
-        <v>3.0668874211670877E-3</v>
+        <v>3.1091001598840605E-3</v>
       </c>
       <c r="O13" s="4">
         <f>STDEV(O2:O11)</f>
-        <v>1.4706420770886269E-2</v>
+        <v>1.4047386741523268E-2</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>55</v>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="14:14" x14ac:dyDescent="0.3">
+      <c r="N21" s="13" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
